--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/测试用例.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/测试用例.xlsx
@@ -529,7 +529,11 @@
           <t>["根据实际到货情况进行记录。", "根据产品规格记录支持的最大硬件规格。"]</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>将机柜的硬件信息及硬件规格记录到2.2.1 测试硬件配置的表格中。</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="b">
         <v>1</v>
@@ -586,7 +590,11 @@
           <t>["根据实际到货情况进行记录。", "根据产品规格记录支持的最大硬件规格。"]</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>将硬件信息及硬件规格记录到2.2.1 测试硬件配置的表格中。</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="b">
         <v>1</v>
@@ -818,7 +826,11 @@
           <t>["设备各部件具备状态指示灯并能针对相应状态变化显示。"]</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>前面板指示灯 前面板指示灯和按钮示意图 前面板指示灯和按钮说明 标识 指示灯和按钮 状态说明 故障诊断数码管 显示---：表示设备正常。 显示故障码：表示设备有部件故障。 故障码的详细信息，请参见《Atlas 900 A3 SuperPoD 超节点 iBMC 用户指南》。 电源按钮/指示灯 电源按钮说明： 上电状态下短按电源按钮，OS正常关机。 上电状态下长按电源按钮6秒钟，可以将设备强制下电。 待上电状态下短按电源按钮，可以进行上电。 电源指示灯说明： 熄灭：设备未上电。 绿色常亮：设备正常上电。 黄色闪烁：电源按钮暂时处于锁定状态，不能进行操作。设备刚上电，管理系统正在启动时，电源按钮会处于锁定状态。 黄色常亮：设备待上电，待机（Standby）状态。 健康状态指示灯 熄灭：设备未上电或处于异常状态。 红色闪烁（1Hz）：系统有严重告警。 红色闪烁（5Hz）：系统有紧急告警。 绿色常亮：设备运转正常。 UID按钮/指示灯 UID按钮： 可通过手动按UID按钮、iBMC命令或者iBMC的WebUI远程管理使灯熄灭、灯亮或闪烁。 短按UID按钮，可以打开/关闭定位灯。 长按UID按钮5秒左右，可以复位管理系统。 指示灯： UID指示灯用于方便地定位待操作的设备。 熄灭：设备未被定位。 蓝色闪烁：设备被重点定位。 蓝色常亮：设备被定位。 - 网口数据传输状态指示灯 黄色（闪烁）：表示有数据正在传输。 熄灭：表示无数据传输。 - 网口连接状态指示灯 绿色（常亮）：表示网络连接正常。 熄灭：表示网络未连接。 - 硬盘指示灯 硬盘指示灯状态说明详细信息请参见表4-2和表4-3。 风扇模块指示灯 熄灭：设备未上电。 绿色（常亮）：表示风扇正常运作。 红色（闪烁）：表示风扇存在告警。 SATA硬盘指示灯说明 硬盘Active指示灯（绿色指示灯） 硬盘Fault指示灯（红色指示灯） 硬盘Locate指示灯（蓝色指示灯） 状态说明 熄灭 熄灭 熄灭 硬盘不在位。 绿色常亮 熄灭 熄灭 硬盘在位。 绿色闪烁（4Hz） 熄灭 熄灭 硬盘处于正常读写状态或重构主盘状态。 绿色常亮 熄灭 蓝色闪烁（1Hz） 硬盘被RAID卡定位。 绿色闪烁（1Hz） 红色闪烁（1Hz） 熄灭 硬盘处于重构从盘状态。 熄灭 红色常亮 熄灭 RAID组中硬盘被拔出。 绿色常亮 红色常亮 熄灭 RAID组中硬盘故障。 NVMe硬盘指示灯说明 硬盘Active指示灯（绿色指示灯） 硬盘Fault指示灯（红色指示灯） 硬盘Locate指示灯（蓝色指示灯） 状态说明 熄灭 熄灭 熄灭 NVMe硬盘不在位。 绿色常亮 熄灭 熄灭 NVMe硬盘在位且无故障。 绿色闪烁（2Hz） 熄灭 熄灭 NVMe硬盘正在进行读写操作。 熄灭 熄灭 蓝色闪烁（2Hz） NVMe硬盘被OS定位或正处于热插过程中。 熄灭 红色闪烁（0.5Hz） 熄灭 NVMe硬盘已完成热拔出流程，允许拔出。 绿色常亮/灭 红色常亮 熄灭 NVMe硬盘故障。</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="b">
         <v>1</v>
@@ -989,7 +1001,11 @@
           <t>["操作系统安装正常。"]</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>说明 若OS在兼容性列表，华为保证该OS和计算节点的兼容性，根据需要可以不进行该方面测试。</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="b">
         <v>1</v>
@@ -1103,7 +1119,11 @@
           <t>["单节点内FP16精度的算力不低于如下值：", "单卡算力：&gt;=752TFLOPS", "单Die算力：&gt;=376TFLOPS"]</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ascend-DMI工具使用请参考：测试工具。</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="b">
         <v>1</v>
@@ -1331,7 +1351,11 @@
           <t>["灵衢交换机接口状态查询正常，为对应端口的实际连接状况。", "覆盖参数面接口状态查询正常，为对应端口的实际连接状况。"]</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>灵衢总线板与灵衢总线和以太板的光口有灵衢交换机接口与参数面接口。</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="b">
         <v>1</v>
@@ -2239,7 +2263,11 @@
           <t>["拔掉其中一块硬盘后，操作系统可以继续正常运行。", "插入同型号的全新硬盘后RAID1自动恢复。"]</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>华为所有的RAID卡，默认策略是开启功能，使用新盘才自动恢复。 如果客户要求使用老盘也可以自动恢复，那就需要修改RAID卡的具体项目。</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="b">
         <v>1</v>
@@ -2402,7 +2430,11 @@
           <t>["系统正常运行，无报错日志。"]</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Ascend-DMI工具使用请参考：测试工具。</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="b">
         <v>1</v>
@@ -3603,11 +3635,7 @@
           <t>["根据实际到货情况进行记录。", "根据产品规格记录支持的最大硬件规格。"]</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>将机柜的硬件信息及硬件规格记录到2.2.1 测试硬件配置的表格中。</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="b">
         <v>1</v>
@@ -3664,11 +3692,7 @@
           <t>["根据实际到货情况进行记录。", "根据产品规格记录支持的最大硬件规格。"]</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>将硬件信息及硬件规格记录到2.2.1 测试硬件配置的表格中。</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="b">
         <v>1</v>
@@ -3900,11 +3924,7 @@
           <t>["设备各部件具备状态指示灯并能针对相应状态变化显示。"]</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>前面板指示灯 前面板指示灯和按钮示意图 前面板指示灯和按钮说明 标识 指示灯和按钮 状态说明 故障诊断数码管 显示---：表示设备正常。 显示故障码：表示设备有部件故障。 故障码的详细信息，请参见《Atlas 900 A3 SuperPoD 超节点 iBMC 用户指南》。 电源按钮/指示灯 电源按钮说明： 上电状态下短按电源按钮，OS正常关机。 上电状态下长按电源按钮6秒钟，可以将设备强制下电。 待上电状态下短按电源按钮，可以进行上电。 电源指示灯说明： 熄灭：设备未上电。 绿色常亮：设备正常上电。 黄色闪烁：电源按钮暂时处于锁定状态，不能进行操作。设备刚上电，管理系统正在启动时，电源按钮会处于锁定状态。 黄色常亮：设备待上电，待机（Standby）状态。 健康状态指示灯 熄灭：设备未上电或处于异常状态。 红色闪烁（1Hz）：系统有严重告警。 红色闪烁（5Hz）：系统有紧急告警。 绿色常亮：设备运转正常。 UID按钮/指示灯 UID按钮： 可通过手动按UID按钮、iBMC命令或者iBMC的WebUI远程管理使灯熄灭、灯亮或闪烁。 短按UID按钮，可以打开/关闭定位灯。 长按UID按钮5秒左右，可以复位管理系统。 指示灯： UID指示灯用于方便地定位待操作的设备。 熄灭：设备未被定位。 蓝色闪烁：设备被重点定位。 蓝色常亮：设备被定位。 - 网口数据传输状态指示灯 黄色（闪烁）：表示有数据正在传输。 熄灭：表示无数据传输。 - 网口连接状态指示灯 绿色（常亮）：表示网络连接正常。 熄灭：表示网络未连接。 - 硬盘指示灯 硬盘指示灯状态说明详细信息请参见表4-2和表4-3。 风扇模块指示灯 熄灭：设备未上电。 绿色（常亮）：表示风扇正常运作。 红色（闪烁）：表示风扇存在告警。 SATA硬盘指示灯说明 硬盘Active指示灯（绿色指示灯） 硬盘Fault指示灯（红色指示灯） 硬盘Locate指示灯（蓝色指示灯） 状态说明 熄灭 熄灭 熄灭 硬盘不在位。 绿色常亮 熄灭 熄灭 硬盘在位。 绿色闪烁（4Hz） 熄灭 熄灭 硬盘处于正常读写状态或重构主盘状态。 绿色常亮 熄灭 蓝色闪烁（1Hz） 硬盘被RAID卡定位。 绿色闪烁（1Hz） 红色闪烁（1Hz） 熄灭 硬盘处于重构从盘状态。 熄灭 红色常亮 熄灭 RAID组中硬盘被拔出。 绿色常亮 红色常亮 熄灭 RAID组中硬盘故障。 NVMe硬盘指示灯说明 硬盘Active指示灯（绿色指示灯） 硬盘Fault指示灯（红色指示灯） 硬盘Locate指示灯（蓝色指示灯） 状态说明 熄灭 熄灭 熄灭 NVMe硬盘不在位。 绿色常亮 熄灭 熄灭 NVMe硬盘在位且无故障。 绿色闪烁（2Hz） 熄灭 熄灭 NVMe硬盘正在进行读写操作。 熄灭 熄灭 蓝色闪烁（2Hz） NVMe硬盘被OS定位或正处于热插过程中。 熄灭 红色闪烁（0.5Hz） 熄灭 NVMe硬盘已完成热拔出流程，允许拔出。 绿色常亮/灭 红色常亮 熄灭 NVMe硬盘故障。</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="b">
         <v>1</v>
@@ -4075,11 +4095,7 @@
           <t>["操作系统安装正常。"]</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>说明 若OS在兼容性列表，华为保证该OS和计算节点的兼容性，根据需要可以不进行该方面测试。</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="b">
         <v>1</v>
@@ -4193,11 +4209,7 @@
           <t>["单节点内FP16精度的算力不低于如下值：", "单卡算力：&gt;=752TFLOPS", "单Die算力：&gt;=376TFLOPS"]</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Ascend-DMI工具使用请参考：测试工具。</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="b">
         <v>1</v>
@@ -4425,11 +4437,7 @@
           <t>["灵衢交换机接口状态查询正常，为对应端口的实际连接状况。", "覆盖参数面接口状态查询正常，为对应端口的实际连接状况。"]</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>灵衢总线板与灵衢总线和以太板的光口有灵衢交换机接口与参数面接口。</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="b">
         <v>1</v>
@@ -5337,11 +5345,7 @@
           <t>["拔掉其中一块硬盘后，操作系统可以继续正常运行。", "插入同型号的全新硬盘后RAID1自动恢复。"]</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>华为所有的RAID卡，默认策略是开启功能，使用新盘才自动恢复。 如果客户要求使用老盘也可以自动恢复，那就需要修改RAID卡的具体项目。</t>
-        </is>
-      </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="b">
         <v>1</v>
@@ -5504,11 +5508,7 @@
           <t>["系统正常运行，无报错日志。"]</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Ascend-DMI工具使用请参考：测试工具。</t>
-        </is>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="b">
         <v>1</v>
